--- a/conservacion_cubicacion.xlsx
+++ b/conservacion_cubicacion.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-18 03:24</t>
+          <t>2026-05-18 03:37</t>
         </is>
       </c>
     </row>
